--- a/database/event/7436/event_7436_evp_summary.xlsx
+++ b/database/event/7436/event_7436_evp_summary.xlsx
@@ -499,7 +499,7 @@
         <v>9.5448</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>6.4314</v>
       </c>
       <c r="D2" t="n">
         <v>3.4345</v>
@@ -545,7 +545,7 @@
         <v>7.3823</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>4.9743</v>
       </c>
       <c r="D3" t="n">
         <v>2.5609</v>
@@ -591,7 +591,7 @@
         <v>6.0353</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>4.0666</v>
       </c>
       <c r="D4" t="n">
         <v>2.0168</v>
@@ -637,7 +637,7 @@
         <v>5.9903</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>4.0363</v>
       </c>
       <c r="D5" t="n">
         <v>1.9986</v>
@@ -683,7 +683,7 @@
         <v>5.9145</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>3.9852</v>
       </c>
       <c r="D6" t="n">
         <v>1.968</v>
@@ -729,7 +729,7 @@
         <v>4.8523</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>3.2695</v>
       </c>
       <c r="D7" t="n">
         <v>1.5389</v>
@@ -775,7 +775,7 @@
         <v>4.6979</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>3.1655</v>
       </c>
       <c r="D8" t="n">
         <v>1.4765</v>
@@ -821,7 +821,7 @@
         <v>4.3906</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>2.9584</v>
       </c>
       <c r="D9" t="n">
         <v>1.3523</v>
@@ -867,7 +867,7 @@
         <v>4.367</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>2.9425</v>
       </c>
       <c r="D10" t="n">
         <v>1.3428</v>
@@ -913,7 +913,7 @@
         <v>4.1798</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>2.8164</v>
       </c>
       <c r="D11" t="n">
         <v>1.2672</v>
@@ -959,7 +959,7 @@
         <v>4.1523</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>2.7979</v>
       </c>
       <c r="D12" t="n">
         <v>1.2561</v>
@@ -1005,7 +1005,7 @@
         <v>4.1129</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>2.7713</v>
       </c>
       <c r="D13" t="n">
         <v>1.2402</v>
@@ -1051,7 +1051,7 @@
         <v>4.0901</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>2.7559</v>
       </c>
       <c r="D14" t="n">
         <v>1.2309</v>
@@ -1097,7 +1097,7 @@
         <v>4.0145</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>2.705</v>
       </c>
       <c r="D15" t="n">
         <v>1.2004</v>
@@ -1143,7 +1143,7 @@
         <v>3.4621</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.3328</v>
       </c>
       <c r="D16" t="n">
         <v>0.9772</v>
@@ -1189,7 +1189,7 @@
         <v>3.3226</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>2.2388</v>
       </c>
       <c r="D17" t="n">
         <v>0.9209000000000001</v>
@@ -1235,7 +1235,7 @@
         <v>3.1573</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>2.1274</v>
       </c>
       <c r="D18" t="n">
         <v>0.8541</v>
@@ -1281,7 +1281,7 @@
         <v>3.0796</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>2.0751</v>
       </c>
       <c r="D19" t="n">
         <v>0.8227</v>
@@ -1327,7 +1327,7 @@
         <v>3.0361</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>2.0457</v>
       </c>
       <c r="D20" t="n">
         <v>0.8052</v>
@@ -1373,7 +1373,7 @@
         <v>2.8387</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1.9127</v>
       </c>
       <c r="D21" t="n">
         <v>0.7254</v>
@@ -1419,7 +1419,7 @@
         <v>2.7886</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1.879</v>
       </c>
       <c r="D22" t="n">
         <v>0.7052</v>
@@ -1465,7 +1465,7 @@
         <v>2.7598</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1.8596</v>
       </c>
       <c r="D23" t="n">
         <v>0.6935</v>
@@ -1511,7 +1511,7 @@
         <v>2.499</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>1.6838</v>
       </c>
       <c r="D24" t="n">
         <v>0.5881999999999999</v>
@@ -1557,7 +1557,7 @@
         <v>2.2774</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>1.5345</v>
       </c>
       <c r="D25" t="n">
         <v>0.4987</v>
@@ -1603,7 +1603,7 @@
         <v>2.1909</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>1.4762</v>
       </c>
       <c r="D26" t="n">
         <v>0.4637</v>
@@ -1649,7 +1649,7 @@
         <v>2.1078</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>1.4203</v>
       </c>
       <c r="D27" t="n">
         <v>0.4301</v>
@@ -1695,7 +1695,7 @@
         <v>2.0759</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>1.3988</v>
       </c>
       <c r="D28" t="n">
         <v>0.4173</v>
@@ -1741,7 +1741,7 @@
         <v>1.6868</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>1.1366</v>
       </c>
       <c r="D29" t="n">
         <v>0.2601</v>
@@ -1787,7 +1787,7 @@
         <v>1.6043</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>1.081</v>
       </c>
       <c r="D30" t="n">
         <v>0.2267</v>
@@ -1833,7 +1833,7 @@
         <v>1.5995</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>1.0778</v>
       </c>
       <c r="D31" t="n">
         <v>0.2248</v>
@@ -1879,7 +1879,7 @@
         <v>1.4551</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>0.9805</v>
       </c>
       <c r="D32" t="n">
         <v>0.1665</v>
@@ -1925,7 +1925,7 @@
         <v>1.4017</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>0.9445</v>
       </c>
       <c r="D33" t="n">
         <v>0.1449</v>
@@ -1971,7 +1971,7 @@
         <v>1.3918</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>0.9378</v>
       </c>
       <c r="D34" t="n">
         <v>0.1409</v>
@@ -2017,7 +2017,7 @@
         <v>1.3703</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>0.9233</v>
       </c>
       <c r="D35" t="n">
         <v>0.1322</v>
@@ -2063,7 +2063,7 @@
         <v>1.3306</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>0.8966</v>
       </c>
       <c r="D36" t="n">
         <v>0.1162</v>
@@ -2109,7 +2109,7 @@
         <v>1.2179</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>0.8206</v>
       </c>
       <c r="D37" t="n">
         <v>0.0706</v>
@@ -2155,7 +2155,7 @@
         <v>1.1634</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>0.7839</v>
       </c>
       <c r="D38" t="n">
         <v>0.0486</v>
@@ -2201,7 +2201,7 @@
         <v>0.9376</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>0.6318</v>
       </c>
       <c r="D39" t="n">
         <v>-0.0426</v>
@@ -2247,7 +2247,7 @@
         <v>0.841</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>0.5667</v>
       </c>
       <c r="D40" t="n">
         <v>-0.08160000000000001</v>
@@ -2293,7 +2293,7 @@
         <v>0.8157</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>0.5496</v>
       </c>
       <c r="D41" t="n">
         <v>-0.09180000000000001</v>
@@ -2339,7 +2339,7 @@
         <v>0.6929999999999999</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>0.4669</v>
       </c>
       <c r="D42" t="n">
         <v>-0.1414</v>
@@ -2385,7 +2385,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>0.3773</v>
       </c>
       <c r="D43" t="n">
         <v>-0.1951</v>
@@ -2431,7 +2431,7 @@
         <v>0.5211</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>0.3511</v>
       </c>
       <c r="D44" t="n">
         <v>-0.2108</v>
@@ -2477,7 +2477,7 @@
         <v>0.4886</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>0.3292</v>
       </c>
       <c r="D45" t="n">
         <v>-0.224</v>
@@ -2523,7 +2523,7 @@
         <v>0.1119</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="D46" t="n">
         <v>-0.3762</v>
@@ -2569,7 +2569,7 @@
         <v>0.0601</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>0.0405</v>
       </c>
       <c r="D47" t="n">
         <v>-0.3971</v>
@@ -2615,7 +2615,7 @@
         <v>-0.1063</v>
       </c>
       <c r="C48" t="n">
-        <v>-0</v>
+        <v>-0.0716</v>
       </c>
       <c r="D48" t="n">
         <v>-0.4643</v>
@@ -2661,7 +2661,7 @@
         <v>-0.1233</v>
       </c>
       <c r="C49" t="n">
-        <v>-0</v>
+        <v>-0.08309999999999999</v>
       </c>
       <c r="D49" t="n">
         <v>-0.4712</v>
@@ -2707,7 +2707,7 @@
         <v>-0.1367</v>
       </c>
       <c r="C50" t="n">
-        <v>-0</v>
+        <v>-0.0921</v>
       </c>
       <c r="D50" t="n">
         <v>-0.4766</v>
@@ -2753,7 +2753,7 @@
         <v>-0.1593</v>
       </c>
       <c r="C51" t="n">
-        <v>-0</v>
+        <v>-0.1073</v>
       </c>
       <c r="D51" t="n">
         <v>-0.4857</v>
@@ -2799,7 +2799,7 @@
         <v>-0.1594</v>
       </c>
       <c r="C52" t="n">
-        <v>-0</v>
+        <v>-0.1074</v>
       </c>
       <c r="D52" t="n">
         <v>-0.4858</v>
@@ -2845,7 +2845,7 @@
         <v>-0.2034</v>
       </c>
       <c r="C53" t="n">
-        <v>-0</v>
+        <v>-0.1371</v>
       </c>
       <c r="D53" t="n">
         <v>-0.5034999999999999</v>
@@ -2891,7 +2891,7 @@
         <v>-0.2867</v>
       </c>
       <c r="C54" t="n">
-        <v>-0</v>
+        <v>-0.1932</v>
       </c>
       <c r="D54" t="n">
         <v>-0.5372</v>
@@ -2937,7 +2937,7 @@
         <v>-0.2964</v>
       </c>
       <c r="C55" t="n">
-        <v>-0</v>
+        <v>-0.1997</v>
       </c>
       <c r="D55" t="n">
         <v>-0.5411</v>
@@ -2983,7 +2983,7 @@
         <v>-0.333</v>
       </c>
       <c r="C56" t="n">
-        <v>-0</v>
+        <v>-0.2244</v>
       </c>
       <c r="D56" t="n">
         <v>-0.5558999999999999</v>
@@ -3029,7 +3029,7 @@
         <v>-0.5336</v>
       </c>
       <c r="C57" t="n">
-        <v>-0</v>
+        <v>-0.3595</v>
       </c>
       <c r="D57" t="n">
         <v>-0.6369</v>
@@ -3075,7 +3075,7 @@
         <v>-0.6902</v>
       </c>
       <c r="C58" t="n">
-        <v>-0</v>
+        <v>-0.4651</v>
       </c>
       <c r="D58" t="n">
         <v>-0.7002</v>
@@ -3121,7 +3121,7 @@
         <v>-0.7060999999999999</v>
       </c>
       <c r="C59" t="n">
-        <v>-0</v>
+        <v>-0.4758</v>
       </c>
       <c r="D59" t="n">
         <v>-0.7066</v>
@@ -3167,7 +3167,7 @@
         <v>-0.7387</v>
       </c>
       <c r="C60" t="n">
-        <v>-0</v>
+        <v>-0.4977</v>
       </c>
       <c r="D60" t="n">
         <v>-0.7198</v>
@@ -3213,7 +3213,7 @@
         <v>-0.7865</v>
       </c>
       <c r="C61" t="n">
-        <v>-0</v>
+        <v>-0.53</v>
       </c>
       <c r="D61" t="n">
         <v>-0.7391</v>
@@ -3259,7 +3259,7 @@
         <v>-0.7966</v>
       </c>
       <c r="C62" t="n">
-        <v>-0</v>
+        <v>-0.5368000000000001</v>
       </c>
       <c r="D62" t="n">
         <v>-0.7432</v>
@@ -3305,7 +3305,7 @@
         <v>-0.9257</v>
       </c>
       <c r="C63" t="n">
-        <v>-0</v>
+        <v>-0.6237</v>
       </c>
       <c r="D63" t="n">
         <v>-0.7953</v>
@@ -3351,7 +3351,7 @@
         <v>-0.9275</v>
       </c>
       <c r="C64" t="n">
-        <v>-0</v>
+        <v>-0.625</v>
       </c>
       <c r="D64" t="n">
         <v>-0.7961</v>
@@ -3397,7 +3397,7 @@
         <v>-0.9571</v>
       </c>
       <c r="C65" t="n">
-        <v>-0</v>
+        <v>-0.6449</v>
       </c>
       <c r="D65" t="n">
         <v>-0.8080000000000001</v>
@@ -3443,7 +3443,7 @@
         <v>-0.9775</v>
       </c>
       <c r="C66" t="n">
-        <v>-0</v>
+        <v>-0.6586</v>
       </c>
       <c r="D66" t="n">
         <v>-0.8163</v>
@@ -3489,7 +3489,7 @@
         <v>-1.0579</v>
       </c>
       <c r="C67" t="n">
-        <v>-0</v>
+        <v>-0.7128</v>
       </c>
       <c r="D67" t="n">
         <v>-0.8487</v>
@@ -3535,7 +3535,7 @@
         <v>-1.089</v>
       </c>
       <c r="C68" t="n">
-        <v>-0</v>
+        <v>-0.7338</v>
       </c>
       <c r="D68" t="n">
         <v>-0.8613</v>
@@ -3581,7 +3581,7 @@
         <v>-1.1128</v>
       </c>
       <c r="C69" t="n">
-        <v>-0</v>
+        <v>-0.7498</v>
       </c>
       <c r="D69" t="n">
         <v>-0.8709</v>
@@ -3627,7 +3627,7 @@
         <v>-1.2068</v>
       </c>
       <c r="C70" t="n">
-        <v>-0</v>
+        <v>-0.8132</v>
       </c>
       <c r="D70" t="n">
         <v>-0.9089</v>
@@ -3673,7 +3673,7 @@
         <v>-1.2905</v>
       </c>
       <c r="C71" t="n">
-        <v>-0</v>
+        <v>-0.8695000000000001</v>
       </c>
       <c r="D71" t="n">
         <v>-0.9427</v>
@@ -3719,7 +3719,7 @@
         <v>-1.4439</v>
       </c>
       <c r="C72" t="n">
-        <v>-0</v>
+        <v>-0.9729</v>
       </c>
       <c r="D72" t="n">
         <v>-1.0047</v>
@@ -3765,7 +3765,7 @@
         <v>-1.7928</v>
       </c>
       <c r="C73" t="n">
-        <v>-0</v>
+        <v>-1.208</v>
       </c>
       <c r="D73" t="n">
         <v>-1.1456</v>
@@ -3811,7 +3811,7 @@
         <v>-1.9484</v>
       </c>
       <c r="C74" t="n">
-        <v>-0</v>
+        <v>-1.3128</v>
       </c>
       <c r="D74" t="n">
         <v>-1.2085</v>
@@ -3857,7 +3857,7 @@
         <v>-1.9587</v>
       </c>
       <c r="C75" t="n">
-        <v>-0</v>
+        <v>-1.3198</v>
       </c>
       <c r="D75" t="n">
         <v>-1.2126</v>
@@ -3903,7 +3903,7 @@
         <v>-2</v>
       </c>
       <c r="C76" t="n">
-        <v>-0</v>
+        <v>-1.3476</v>
       </c>
       <c r="D76" t="n">
         <v>-1.2293</v>
@@ -3949,7 +3949,7 @@
         <v>-2</v>
       </c>
       <c r="C77" t="n">
-        <v>-0</v>
+        <v>-1.3476</v>
       </c>
       <c r="D77" t="n">
         <v>-1.2293</v>
@@ -3995,7 +3995,7 @@
         <v>-2.6555</v>
       </c>
       <c r="C78" t="n">
-        <v>-0</v>
+        <v>-1.7893</v>
       </c>
       <c r="D78" t="n">
         <v>-1.4941</v>
@@ -4041,7 +4041,7 @@
         <v>-2.9099</v>
       </c>
       <c r="C79" t="n">
-        <v>-0</v>
+        <v>-1.9607</v>
       </c>
       <c r="D79" t="n">
         <v>-1.5969</v>
@@ -4087,7 +4087,7 @@
         <v>-3.0277</v>
       </c>
       <c r="C80" t="n">
-        <v>-0</v>
+        <v>-2.0401</v>
       </c>
       <c r="D80" t="n">
         <v>-1.6445</v>
@@ -4133,7 +4133,7 @@
         <v>-3.5529</v>
       </c>
       <c r="C81" t="n">
-        <v>-0</v>
+        <v>-2.394</v>
       </c>
       <c r="D81" t="n">
         <v>-1.8567</v>

--- a/database/event/7436/event_7436_evp_summary.xlsx
+++ b/database/event/7436/event_7436_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>6.4314</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4345</v>
+        <v>3.3587</v>
       </c>
       <c r="E2" t="n">
         <v>9.5448</v>
@@ -548,7 +548,7 @@
         <v>4.9743</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5609</v>
+        <v>2.4972</v>
       </c>
       <c r="E3" t="n">
         <v>7.3823</v>
@@ -594,7 +594,7 @@
         <v>4.0666</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0168</v>
+        <v>1.9606</v>
       </c>
       <c r="E4" t="n">
         <v>6.0353</v>
@@ -634,25 +634,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.9903</v>
+        <v>5.9676</v>
       </c>
       <c r="C5" t="n">
-        <v>4.0363</v>
+        <v>4.021</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9986</v>
+        <v>1.9336</v>
       </c>
       <c r="E5" t="n">
-        <v>5.9903</v>
+        <v>5.9676</v>
       </c>
       <c r="F5" t="n">
-        <v>4.5199</v>
+        <v>4.4972</v>
       </c>
       <c r="G5" t="n">
         <v>1.4704</v>
       </c>
       <c r="H5" t="n">
-        <v>4.7842</v>
+        <v>4.7486</v>
       </c>
       <c r="I5" t="n">
         <v>4.8289</v>
@@ -686,7 +686,7 @@
         <v>3.9852</v>
       </c>
       <c r="D6" t="n">
-        <v>1.968</v>
+        <v>1.9124</v>
       </c>
       <c r="E6" t="n">
         <v>5.9145</v>
@@ -732,7 +732,7 @@
         <v>3.2695</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5389</v>
+        <v>1.4892</v>
       </c>
       <c r="E7" t="n">
         <v>4.8523</v>
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.6979</v>
+        <v>4.6732</v>
       </c>
       <c r="C8" t="n">
-        <v>3.1655</v>
+        <v>3.1488</v>
       </c>
       <c r="D8" t="n">
-        <v>1.4765</v>
+        <v>1.4179</v>
       </c>
       <c r="E8" t="n">
-        <v>4.6979</v>
+        <v>4.6732</v>
       </c>
       <c r="F8" t="n">
-        <v>4.7803</v>
+        <v>4.7556</v>
       </c>
       <c r="G8" t="n">
         <v>-0.0824</v>
       </c>
       <c r="H8" t="n">
-        <v>5.1924</v>
+        <v>5.1537</v>
       </c>
       <c r="I8" t="n">
         <v>5.2408</v>
@@ -824,7 +824,7 @@
         <v>2.9584</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3523</v>
+        <v>1.3053</v>
       </c>
       <c r="E9" t="n">
         <v>4.3906</v>
@@ -864,25 +864,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.367</v>
+        <v>4.3275</v>
       </c>
       <c r="C10" t="n">
-        <v>2.9425</v>
+        <v>2.9159</v>
       </c>
       <c r="D10" t="n">
-        <v>1.3428</v>
+        <v>1.2802</v>
       </c>
       <c r="E10" t="n">
-        <v>4.367</v>
+        <v>4.3275</v>
       </c>
       <c r="F10" t="n">
-        <v>3.5477</v>
+        <v>3.5082</v>
       </c>
       <c r="G10" t="n">
         <v>0.8193</v>
       </c>
       <c r="H10" t="n">
-        <v>3.5477</v>
+        <v>3.5082</v>
       </c>
       <c r="I10" t="n">
         <v>3.5975</v>
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.1798</v>
+        <v>4.1706</v>
       </c>
       <c r="C11" t="n">
-        <v>2.8164</v>
+        <v>2.8102</v>
       </c>
       <c r="D11" t="n">
-        <v>1.2672</v>
+        <v>1.2177</v>
       </c>
       <c r="E11" t="n">
-        <v>4.1798</v>
+        <v>4.1706</v>
       </c>
       <c r="F11" t="n">
-        <v>2.4691</v>
+        <v>2.4599</v>
       </c>
       <c r="G11" t="n">
         <v>1.7107</v>
       </c>
       <c r="H11" t="n">
-        <v>2.4691</v>
+        <v>2.4599</v>
       </c>
       <c r="I11" t="n">
         <v>2.4806</v>
@@ -962,7 +962,7 @@
         <v>2.7979</v>
       </c>
       <c r="D12" t="n">
-        <v>1.2561</v>
+        <v>1.2104</v>
       </c>
       <c r="E12" t="n">
         <v>4.1523</v>
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4.1129</v>
+        <v>4.0914</v>
       </c>
       <c r="C13" t="n">
-        <v>2.7713</v>
+        <v>2.7568</v>
       </c>
       <c r="D13" t="n">
-        <v>1.2402</v>
+        <v>1.1861</v>
       </c>
       <c r="E13" t="n">
-        <v>4.1129</v>
+        <v>4.0914</v>
       </c>
       <c r="F13" t="n">
-        <v>4.3669</v>
+        <v>4.3454</v>
       </c>
       <c r="G13" t="n">
         <v>-0.254</v>
       </c>
       <c r="H13" t="n">
-        <v>4.5443</v>
+        <v>4.5105</v>
       </c>
       <c r="I13" t="n">
         <v>4.5867</v>
@@ -1054,7 +1054,7 @@
         <v>2.7559</v>
       </c>
       <c r="D14" t="n">
-        <v>1.2309</v>
+        <v>1.1856</v>
       </c>
       <c r="E14" t="n">
         <v>4.0901</v>
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.0145</v>
+        <v>4.0063</v>
       </c>
       <c r="C15" t="n">
-        <v>2.705</v>
+        <v>2.6995</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2004</v>
+        <v>1.1522</v>
       </c>
       <c r="E15" t="n">
-        <v>4.0145</v>
+        <v>4.0063</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2029</v>
+        <v>2.1947</v>
       </c>
       <c r="G15" t="n">
         <v>1.8116</v>
       </c>
       <c r="H15" t="n">
-        <v>2.2029</v>
+        <v>2.1947</v>
       </c>
       <c r="I15" t="n">
         <v>2.2132</v>
@@ -1140,25 +1140,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.4621</v>
+        <v>3.4492</v>
       </c>
       <c r="C16" t="n">
-        <v>2.3328</v>
+        <v>2.3241</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9772</v>
+        <v>0.9303</v>
       </c>
       <c r="E16" t="n">
-        <v>3.4621</v>
+        <v>3.4492</v>
       </c>
       <c r="F16" t="n">
-        <v>3.4621</v>
+        <v>3.4492</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>3.4621</v>
+        <v>3.4492</v>
       </c>
       <c r="I16" t="n">
         <v>3.4782</v>
@@ -1186,25 +1186,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.3226</v>
+        <v>3.3102</v>
       </c>
       <c r="C17" t="n">
-        <v>2.2388</v>
+        <v>2.2304</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9209000000000001</v>
+        <v>0.8749</v>
       </c>
       <c r="E17" t="n">
-        <v>3.3226</v>
+        <v>3.3102</v>
       </c>
       <c r="F17" t="n">
-        <v>3.3226</v>
+        <v>3.3102</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>3.3226</v>
+        <v>3.3102</v>
       </c>
       <c r="I17" t="n">
         <v>3.3381</v>
@@ -1232,25 +1232,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.1573</v>
+        <v>3.1275</v>
       </c>
       <c r="C18" t="n">
-        <v>2.1274</v>
+        <v>2.1073</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8541</v>
+        <v>0.8021</v>
       </c>
       <c r="E18" t="n">
-        <v>3.1573</v>
+        <v>3.1275</v>
       </c>
       <c r="F18" t="n">
-        <v>4.0037</v>
+        <v>3.9739</v>
       </c>
       <c r="G18" t="n">
         <v>-0.8464</v>
       </c>
       <c r="H18" t="n">
-        <v>4.0037</v>
+        <v>3.9739</v>
       </c>
       <c r="I18" t="n">
         <v>4.041</v>
@@ -1278,25 +1278,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.0796</v>
+        <v>3.0496</v>
       </c>
       <c r="C19" t="n">
-        <v>2.0751</v>
+        <v>2.0548</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8227</v>
+        <v>0.7711</v>
       </c>
       <c r="E19" t="n">
-        <v>3.0796</v>
+        <v>3.0496</v>
       </c>
       <c r="F19" t="n">
-        <v>2.6881</v>
+        <v>2.6581</v>
       </c>
       <c r="G19" t="n">
         <v>0.3915</v>
       </c>
       <c r="H19" t="n">
-        <v>2.6881</v>
+        <v>2.6581</v>
       </c>
       <c r="I19" t="n">
         <v>2.7258</v>
@@ -1330,7 +1330,7 @@
         <v>2.0457</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8052</v>
+        <v>0.7657</v>
       </c>
       <c r="E20" t="n">
         <v>3.0361</v>
@@ -1376,7 +1376,7 @@
         <v>1.9127</v>
       </c>
       <c r="D21" t="n">
-        <v>0.7254</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="E21" t="n">
         <v>2.8387</v>
@@ -1422,7 +1422,7 @@
         <v>1.879</v>
       </c>
       <c r="D22" t="n">
-        <v>0.7052</v>
+        <v>0.6671</v>
       </c>
       <c r="E22" t="n">
         <v>2.7886</v>
@@ -1468,7 +1468,7 @@
         <v>1.8596</v>
       </c>
       <c r="D23" t="n">
-        <v>0.6935</v>
+        <v>0.6556</v>
       </c>
       <c r="E23" t="n">
         <v>2.7598</v>
@@ -1514,7 +1514,7 @@
         <v>1.6838</v>
       </c>
       <c r="D24" t="n">
-        <v>0.5881999999999999</v>
+        <v>0.5517</v>
       </c>
       <c r="E24" t="n">
         <v>2.499</v>
@@ -1560,7 +1560,7 @@
         <v>1.5345</v>
       </c>
       <c r="D25" t="n">
-        <v>0.4987</v>
+        <v>0.4634</v>
       </c>
       <c r="E25" t="n">
         <v>2.2774</v>
@@ -1606,7 +1606,7 @@
         <v>1.4762</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4637</v>
+        <v>0.4289</v>
       </c>
       <c r="E26" t="n">
         <v>2.1909</v>
@@ -1646,25 +1646,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.1078</v>
+        <v>2.0837</v>
       </c>
       <c r="C27" t="n">
-        <v>1.4203</v>
+        <v>1.404</v>
       </c>
       <c r="D27" t="n">
-        <v>0.4301</v>
+        <v>0.3862</v>
       </c>
       <c r="E27" t="n">
-        <v>2.1078</v>
+        <v>2.0837</v>
       </c>
       <c r="F27" t="n">
-        <v>2.1557</v>
+        <v>2.1316</v>
       </c>
       <c r="G27" t="n">
         <v>-0.0479</v>
       </c>
       <c r="H27" t="n">
-        <v>2.1557</v>
+        <v>2.1316</v>
       </c>
       <c r="I27" t="n">
         <v>2.1859</v>
@@ -1698,7 +1698,7 @@
         <v>1.3988</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4173</v>
+        <v>0.3831</v>
       </c>
       <c r="E28" t="n">
         <v>2.0759</v>
@@ -1738,25 +1738,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.6868</v>
+        <v>1.6806</v>
       </c>
       <c r="C29" t="n">
-        <v>1.1366</v>
+        <v>1.1324</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2601</v>
+        <v>0.2256</v>
       </c>
       <c r="E29" t="n">
-        <v>1.6868</v>
+        <v>1.6806</v>
       </c>
       <c r="F29" t="n">
-        <v>1.6868</v>
+        <v>1.6806</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.6868</v>
+        <v>1.6806</v>
       </c>
       <c r="I29" t="n">
         <v>1.6947</v>
@@ -1790,7 +1790,7 @@
         <v>1.081</v>
       </c>
       <c r="D30" t="n">
-        <v>0.2267</v>
+        <v>0.1952</v>
       </c>
       <c r="E30" t="n">
         <v>1.6043</v>
@@ -1836,7 +1836,7 @@
         <v>1.0778</v>
       </c>
       <c r="D31" t="n">
-        <v>0.2248</v>
+        <v>0.1933</v>
       </c>
       <c r="E31" t="n">
         <v>1.5995</v>
@@ -1882,7 +1882,7 @@
         <v>0.9805</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1665</v>
+        <v>0.1358</v>
       </c>
       <c r="E32" t="n">
         <v>1.4551</v>
@@ -1928,7 +1928,7 @@
         <v>0.9445</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1449</v>
+        <v>0.1145</v>
       </c>
       <c r="E33" t="n">
         <v>1.4017</v>
@@ -1968,25 +1968,25 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.3918</v>
+        <v>1.3864</v>
       </c>
       <c r="C34" t="n">
-        <v>0.9378</v>
+        <v>0.9342</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1409</v>
+        <v>0.1084</v>
       </c>
       <c r="E34" t="n">
-        <v>1.3918</v>
+        <v>1.3864</v>
       </c>
       <c r="F34" t="n">
-        <v>1.4523</v>
+        <v>1.4469</v>
       </c>
       <c r="G34" t="n">
         <v>-0.0605</v>
       </c>
       <c r="H34" t="n">
-        <v>1.4523</v>
+        <v>1.4469</v>
       </c>
       <c r="I34" t="n">
         <v>1.4591</v>
@@ -2020,7 +2020,7 @@
         <v>0.9233</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1322</v>
+        <v>0.102</v>
       </c>
       <c r="E35" t="n">
         <v>1.3703</v>
@@ -2066,7 +2066,7 @@
         <v>0.8966</v>
       </c>
       <c r="D36" t="n">
-        <v>0.1162</v>
+        <v>0.0862</v>
       </c>
       <c r="E36" t="n">
         <v>1.3306</v>
@@ -2112,7 +2112,7 @@
         <v>0.8206</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0706</v>
+        <v>0.0413</v>
       </c>
       <c r="E37" t="n">
         <v>1.2179</v>
@@ -2158,7 +2158,7 @@
         <v>0.7839</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0486</v>
+        <v>0.0196</v>
       </c>
       <c r="E38" t="n">
         <v>1.1634</v>
@@ -2204,7 +2204,7 @@
         <v>0.6318</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.0426</v>
+        <v>-0.0704</v>
       </c>
       <c r="E39" t="n">
         <v>0.9376</v>
@@ -2244,25 +2244,25 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.841</v>
+        <v>0.8378</v>
       </c>
       <c r="C40" t="n">
-        <v>0.5667</v>
+        <v>0.5645</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.08160000000000001</v>
+        <v>-0.1101</v>
       </c>
       <c r="E40" t="n">
-        <v>0.841</v>
+        <v>0.8378</v>
       </c>
       <c r="F40" t="n">
-        <v>0.841</v>
+        <v>0.8378</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.841</v>
+        <v>0.8378</v>
       </c>
       <c r="I40" t="n">
         <v>0.8449</v>
@@ -2296,7 +2296,7 @@
         <v>0.5496</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.09180000000000001</v>
+        <v>-0.1189</v>
       </c>
       <c r="E41" t="n">
         <v>0.8157</v>
@@ -2342,7 +2342,7 @@
         <v>0.4669</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.1414</v>
+        <v>-0.1678</v>
       </c>
       <c r="E42" t="n">
         <v>0.6929999999999999</v>
@@ -2388,7 +2388,7 @@
         <v>0.3773</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.1951</v>
+        <v>-0.2208</v>
       </c>
       <c r="E43" t="n">
         <v>0.5600000000000001</v>
@@ -2434,7 +2434,7 @@
         <v>0.3511</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.2108</v>
+        <v>-0.2363</v>
       </c>
       <c r="E44" t="n">
         <v>0.5211</v>
@@ -2474,25 +2474,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.4886</v>
+        <v>0.4868</v>
       </c>
       <c r="C45" t="n">
-        <v>0.3292</v>
+        <v>0.328</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.224</v>
+        <v>-0.25</v>
       </c>
       <c r="E45" t="n">
-        <v>0.4886</v>
+        <v>0.4868</v>
       </c>
       <c r="F45" t="n">
-        <v>0.4886</v>
+        <v>0.4868</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.4886</v>
+        <v>0.4868</v>
       </c>
       <c r="I45" t="n">
         <v>0.4909</v>
@@ -2526,7 +2526,7 @@
         <v>0.07539999999999999</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3762</v>
+        <v>-0.3993</v>
       </c>
       <c r="E46" t="n">
         <v>0.1119</v>
@@ -2572,7 +2572,7 @@
         <v>0.0405</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3971</v>
+        <v>-0.42</v>
       </c>
       <c r="E47" t="n">
         <v>0.0601</v>
@@ -2618,7 +2618,7 @@
         <v>-0.0716</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.4643</v>
+        <v>-0.4863</v>
       </c>
       <c r="E48" t="n">
         <v>-0.1063</v>
@@ -2664,7 +2664,7 @@
         <v>-0.08309999999999999</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.4712</v>
+        <v>-0.493</v>
       </c>
       <c r="E49" t="n">
         <v>-0.1233</v>
@@ -2710,7 +2710,7 @@
         <v>-0.0921</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.4766</v>
+        <v>-0.4984</v>
       </c>
       <c r="E50" t="n">
         <v>-0.1367</v>
@@ -2756,7 +2756,7 @@
         <v>-0.1073</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4857</v>
+        <v>-0.5074</v>
       </c>
       <c r="E51" t="n">
         <v>-0.1593</v>
@@ -2796,25 +2796,25 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.1594</v>
+        <v>-0.1679</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.1074</v>
+        <v>-0.1131</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.4858</v>
+        <v>-0.5108</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.1594</v>
+        <v>-0.1679</v>
       </c>
       <c r="F52" t="n">
-        <v>0.7567</v>
+        <v>0.7482</v>
       </c>
       <c r="G52" t="n">
         <v>-0.9161</v>
       </c>
       <c r="H52" t="n">
-        <v>0.7567</v>
+        <v>0.7482</v>
       </c>
       <c r="I52" t="n">
         <v>0.7673</v>
@@ -2848,7 +2848,7 @@
         <v>-0.1371</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.5034999999999999</v>
+        <v>-0.5249</v>
       </c>
       <c r="E53" t="n">
         <v>-0.2034</v>
@@ -2894,7 +2894,7 @@
         <v>-0.1932</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.5372</v>
+        <v>-0.5581</v>
       </c>
       <c r="E54" t="n">
         <v>-0.2867</v>
@@ -2940,7 +2940,7 @@
         <v>-0.1997</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5411</v>
+        <v>-0.5620000000000001</v>
       </c>
       <c r="E55" t="n">
         <v>-0.2964</v>
@@ -2986,7 +2986,7 @@
         <v>-0.2244</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5558999999999999</v>
+        <v>-0.5766</v>
       </c>
       <c r="E56" t="n">
         <v>-0.333</v>
@@ -3032,7 +3032,7 @@
         <v>-0.3595</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.6369</v>
+        <v>-0.6565</v>
       </c>
       <c r="E57" t="n">
         <v>-0.5336</v>
@@ -3078,7 +3078,7 @@
         <v>-0.4651</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.7002</v>
+        <v>-0.7189</v>
       </c>
       <c r="E58" t="n">
         <v>-0.6902</v>
@@ -3124,7 +3124,7 @@
         <v>-0.4758</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.7066</v>
+        <v>-0.7252</v>
       </c>
       <c r="E59" t="n">
         <v>-0.7060999999999999</v>
@@ -3170,7 +3170,7 @@
         <v>-0.4977</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.7198</v>
+        <v>-0.7382</v>
       </c>
       <c r="E60" t="n">
         <v>-0.7387</v>
@@ -3216,7 +3216,7 @@
         <v>-0.53</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.7391</v>
+        <v>-0.7573</v>
       </c>
       <c r="E61" t="n">
         <v>-0.7865</v>
@@ -3262,7 +3262,7 @@
         <v>-0.5368000000000001</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.7432</v>
+        <v>-0.7613</v>
       </c>
       <c r="E62" t="n">
         <v>-0.7966</v>
@@ -3308,7 +3308,7 @@
         <v>-0.6237</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7953</v>
+        <v>-0.8127</v>
       </c>
       <c r="E63" t="n">
         <v>-0.9257</v>
@@ -3354,7 +3354,7 @@
         <v>-0.625</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7961</v>
+        <v>-0.8134</v>
       </c>
       <c r="E64" t="n">
         <v>-0.9275</v>
@@ -3400,7 +3400,7 @@
         <v>-0.6449</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.8080000000000001</v>
+        <v>-0.8252</v>
       </c>
       <c r="E65" t="n">
         <v>-0.9571</v>
@@ -3446,7 +3446,7 @@
         <v>-0.6586</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.8163</v>
+        <v>-0.8333</v>
       </c>
       <c r="E66" t="n">
         <v>-0.9775</v>
@@ -3492,7 +3492,7 @@
         <v>-0.7128</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.8487</v>
+        <v>-0.8653999999999999</v>
       </c>
       <c r="E67" t="n">
         <v>-1.0579</v>
@@ -3538,7 +3538,7 @@
         <v>-0.7338</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8613</v>
+        <v>-0.8778</v>
       </c>
       <c r="E68" t="n">
         <v>-1.089</v>
@@ -3578,25 +3578,25 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-1.1128</v>
+        <v>-1.106</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.7498</v>
+        <v>-0.7452</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8709</v>
+        <v>-0.8845</v>
       </c>
       <c r="E69" t="n">
-        <v>-1.1128</v>
+        <v>-1.106</v>
       </c>
       <c r="F69" t="n">
-        <v>-1.8275</v>
+        <v>-1.8207</v>
       </c>
       <c r="G69" t="n">
         <v>0.7147</v>
       </c>
       <c r="H69" t="n">
-        <v>-1.8275</v>
+        <v>-1.8207</v>
       </c>
       <c r="I69" t="n">
         <v>-1.836</v>
@@ -3630,7 +3630,7 @@
         <v>-0.8132</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9089</v>
+        <v>-0.9247</v>
       </c>
       <c r="E70" t="n">
         <v>-1.2068</v>
@@ -3676,7 +3676,7 @@
         <v>-0.8695000000000001</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9427</v>
+        <v>-0.958</v>
       </c>
       <c r="E71" t="n">
         <v>-1.2905</v>
@@ -3722,7 +3722,7 @@
         <v>-0.9729</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.0047</v>
+        <v>-1.0192</v>
       </c>
       <c r="E72" t="n">
         <v>-1.4439</v>
@@ -3762,25 +3762,25 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.7928</v>
+        <v>-1.7729</v>
       </c>
       <c r="C73" t="n">
-        <v>-1.208</v>
+        <v>-1.1946</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.1456</v>
+        <v>-1.1502</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.7928</v>
+        <v>-1.7729</v>
       </c>
       <c r="F73" t="n">
-        <v>-1.7865</v>
+        <v>-1.7666</v>
       </c>
       <c r="G73" t="n">
         <v>-0.0063</v>
       </c>
       <c r="H73" t="n">
-        <v>-1.7865</v>
+        <v>-1.7666</v>
       </c>
       <c r="I73" t="n">
         <v>-1.8116</v>
@@ -3814,7 +3814,7 @@
         <v>-1.3128</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.2085</v>
+        <v>-1.2202</v>
       </c>
       <c r="E74" t="n">
         <v>-1.9484</v>
@@ -3860,7 +3860,7 @@
         <v>-1.3198</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.2126</v>
+        <v>-1.2243</v>
       </c>
       <c r="E75" t="n">
         <v>-1.9587</v>
@@ -3906,7 +3906,7 @@
         <v>-1.3476</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.2293</v>
+        <v>-1.2407</v>
       </c>
       <c r="E76" t="n">
         <v>-2</v>
@@ -3952,7 +3952,7 @@
         <v>-1.3476</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.2293</v>
+        <v>-1.2407</v>
       </c>
       <c r="E77" t="n">
         <v>-2</v>
@@ -3992,25 +3992,25 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-2.6555</v>
+        <v>-2.6381</v>
       </c>
       <c r="C78" t="n">
-        <v>-1.7893</v>
+        <v>-1.7776</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.4941</v>
+        <v>-1.4949</v>
       </c>
       <c r="E78" t="n">
-        <v>-2.6555</v>
+        <v>-2.6381</v>
       </c>
       <c r="F78" t="n">
-        <v>-2.3297</v>
+        <v>-2.3123</v>
       </c>
       <c r="G78" t="n">
         <v>-0.3258</v>
       </c>
       <c r="H78" t="n">
-        <v>-2.3297</v>
+        <v>-2.3123</v>
       </c>
       <c r="I78" t="n">
         <v>-2.3514</v>
@@ -4044,7 +4044,7 @@
         <v>-1.9607</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.5969</v>
+        <v>-1.6032</v>
       </c>
       <c r="E79" t="n">
         <v>-2.9099</v>
@@ -4090,7 +4090,7 @@
         <v>-2.0401</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.6445</v>
+        <v>-1.6501</v>
       </c>
       <c r="E80" t="n">
         <v>-3.0277</v>
@@ -4130,25 +4130,25 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-3.5529</v>
+        <v>-3.5471</v>
       </c>
       <c r="C81" t="n">
-        <v>-2.394</v>
+        <v>-2.3901</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.8567</v>
+        <v>-1.8571</v>
       </c>
       <c r="E81" t="n">
-        <v>-3.5529</v>
+        <v>-3.5471</v>
       </c>
       <c r="F81" t="n">
-        <v>-1.5529</v>
+        <v>-1.5471</v>
       </c>
       <c r="G81" t="n">
         <v>-2</v>
       </c>
       <c r="H81" t="n">
-        <v>-1.5529</v>
+        <v>-1.5471</v>
       </c>
       <c r="I81" t="n">
         <v>-1.5601</v>

--- a/database/event/7436/event_7436_evp_summary.xlsx
+++ b/database/event/7436/event_7436_evp_summary.xlsx
@@ -496,16 +496,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.6159</v>
+        <v>8.855</v>
       </c>
       <c r="C2" t="n">
-        <v>5.8055</v>
+        <v>5.9666</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2979</v>
+        <v>3.3415</v>
       </c>
       <c r="E2" t="n">
-        <v>8.6159</v>
+        <v>8.855</v>
       </c>
       <c r="F2" t="n">
         <v>3.3935</v>
@@ -542,16 +542,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.1167</v>
+        <v>7.2745</v>
       </c>
       <c r="C3" t="n">
-        <v>4.7953</v>
+        <v>4.9016</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6155</v>
+        <v>2.6355</v>
       </c>
       <c r="E3" t="n">
-        <v>7.1167</v>
+        <v>7.2745</v>
       </c>
       <c r="F3" t="n">
         <v>4.5807</v>
@@ -588,16 +588,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.3921</v>
+        <v>6.6361</v>
       </c>
       <c r="C4" t="n">
-        <v>4.3071</v>
+        <v>4.4715</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2856</v>
+        <v>2.3504</v>
       </c>
       <c r="E4" t="n">
-        <v>6.3921</v>
+        <v>6.6361</v>
       </c>
       <c r="F4" t="n">
         <v>4.5807</v>
@@ -634,16 +634,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.8194</v>
+        <v>5.9761</v>
       </c>
       <c r="C5" t="n">
-        <v>3.9212</v>
+        <v>4.0267</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0249</v>
+        <v>2.0556</v>
       </c>
       <c r="E5" t="n">
-        <v>5.8194</v>
+        <v>5.9761</v>
       </c>
       <c r="F5" t="n">
         <v>4.3024</v>
@@ -680,16 +680,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.7561</v>
+        <v>5.9047</v>
       </c>
       <c r="C6" t="n">
-        <v>3.8785</v>
+        <v>3.9786</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9961</v>
+        <v>2.0237</v>
       </c>
       <c r="E6" t="n">
-        <v>5.7561</v>
+        <v>5.9047</v>
       </c>
       <c r="F6" t="n">
         <v>4.2314</v>
@@ -722,47 +722,47 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>jL</t>
+          <t>ewjerkz</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.6397</v>
+        <v>4.7597</v>
       </c>
       <c r="C7" t="n">
-        <v>3.1263</v>
+        <v>3.2071</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4879</v>
+        <v>1.5122</v>
       </c>
       <c r="E7" t="n">
-        <v>4.6397</v>
+        <v>4.7597</v>
       </c>
       <c r="F7" t="n">
-        <v>4.5348</v>
+        <v>2.8608</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1049</v>
+        <v>1.6577</v>
       </c>
       <c r="H7" t="n">
-        <v>10.0679</v>
+        <v>3.5364</v>
       </c>
       <c r="I7" t="n">
-        <v>5.4366</v>
+        <v>3.6275</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1049</v>
+        <v>1.6577</v>
       </c>
       <c r="K7" t="n">
-        <v>127</v>
+        <v>169</v>
       </c>
       <c r="L7" t="n">
-        <v>171</v>
+        <v>110</v>
       </c>
       <c r="M7" t="n">
-        <v>5.5415</v>
+        <v>5.2852</v>
       </c>
       <c r="N7" t="n">
-        <v>298</v>
+        <v>279</v>
       </c>
     </row>
     <row r="8">
@@ -772,16 +772,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.6034</v>
+        <v>4.7094</v>
       </c>
       <c r="C8" t="n">
-        <v>3.1018</v>
+        <v>3.1732</v>
       </c>
       <c r="D8" t="n">
-        <v>1.4714</v>
+        <v>1.4898</v>
       </c>
       <c r="E8" t="n">
-        <v>4.6034</v>
+        <v>4.7094</v>
       </c>
       <c r="F8" t="n">
         <v>4.0377</v>
@@ -814,81 +814,81 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ewjerkz</t>
+          <t>jL</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.5184</v>
+        <v>4.6985</v>
       </c>
       <c r="C9" t="n">
-        <v>3.0445</v>
+        <v>3.1659</v>
       </c>
       <c r="D9" t="n">
-        <v>1.4327</v>
+        <v>1.4849</v>
       </c>
       <c r="E9" t="n">
-        <v>4.5184</v>
+        <v>4.6985</v>
       </c>
       <c r="F9" t="n">
-        <v>2.8608</v>
+        <v>4.5348</v>
       </c>
       <c r="G9" t="n">
-        <v>1.6577</v>
+        <v>0.1049</v>
       </c>
       <c r="H9" t="n">
-        <v>3.5364</v>
+        <v>10.0679</v>
       </c>
       <c r="I9" t="n">
-        <v>3.6275</v>
+        <v>5.4366</v>
       </c>
       <c r="J9" t="n">
-        <v>1.6577</v>
+        <v>0.1049</v>
       </c>
       <c r="K9" t="n">
-        <v>169</v>
+        <v>127</v>
       </c>
       <c r="L9" t="n">
-        <v>110</v>
+        <v>171</v>
       </c>
       <c r="M9" t="n">
-        <v>5.2852</v>
+        <v>5.5415</v>
       </c>
       <c r="N9" t="n">
-        <v>279</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>malbsMd</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.3717</v>
+        <v>4.5053</v>
       </c>
       <c r="C10" t="n">
-        <v>2.9457</v>
+        <v>3.0357</v>
       </c>
       <c r="D10" t="n">
-        <v>1.3659</v>
+        <v>1.3986</v>
       </c>
       <c r="E10" t="n">
-        <v>4.3717</v>
+        <v>4.5053</v>
       </c>
       <c r="F10" t="n">
-        <v>4.285</v>
+        <v>4.2991</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0867</v>
+        <v>0.0255</v>
       </c>
       <c r="H10" t="n">
-        <v>6.6537</v>
+        <v>6.6844</v>
       </c>
       <c r="I10" t="n">
-        <v>7.001</v>
+        <v>7.0333</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0867</v>
+        <v>0.0255</v>
       </c>
       <c r="K10" t="n">
         <v>157</v>
@@ -897,7 +897,7 @@
         <v>43</v>
       </c>
       <c r="M10" t="n">
-        <v>7.0877</v>
+        <v>7.0588</v>
       </c>
       <c r="N10" t="n">
         <v>200</v>
@@ -906,35 +906,35 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>malbsMd</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.3246</v>
+        <v>4.5011</v>
       </c>
       <c r="C11" t="n">
-        <v>2.914</v>
+        <v>3.0329</v>
       </c>
       <c r="D11" t="n">
-        <v>1.3444</v>
+        <v>1.3967</v>
       </c>
       <c r="E11" t="n">
-        <v>4.3246</v>
+        <v>4.5011</v>
       </c>
       <c r="F11" t="n">
-        <v>4.2991</v>
+        <v>4.285</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0255</v>
+        <v>0.0867</v>
       </c>
       <c r="H11" t="n">
-        <v>6.6844</v>
+        <v>6.6537</v>
       </c>
       <c r="I11" t="n">
-        <v>7.0333</v>
+        <v>7.001</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0255</v>
+        <v>0.0867</v>
       </c>
       <c r="K11" t="n">
         <v>157</v>
@@ -943,7 +943,7 @@
         <v>43</v>
       </c>
       <c r="M11" t="n">
-        <v>7.0588</v>
+        <v>7.0877</v>
       </c>
       <c r="N11" t="n">
         <v>200</v>
@@ -956,16 +956,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.1768</v>
+        <v>4.1464</v>
       </c>
       <c r="C12" t="n">
-        <v>2.8144</v>
+        <v>2.7939</v>
       </c>
       <c r="D12" t="n">
-        <v>1.2772</v>
+        <v>1.2383</v>
       </c>
       <c r="E12" t="n">
-        <v>4.1768</v>
+        <v>4.1464</v>
       </c>
       <c r="F12" t="n">
         <v>2.6449</v>
@@ -1002,16 +1002,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.8218</v>
+        <v>3.8703</v>
       </c>
       <c r="C13" t="n">
-        <v>2.5752</v>
+        <v>2.6078</v>
       </c>
       <c r="D13" t="n">
-        <v>1.1156</v>
+        <v>1.115</v>
       </c>
       <c r="E13" t="n">
-        <v>3.8218</v>
+        <v>3.8703</v>
       </c>
       <c r="F13" t="n">
         <v>2.3049</v>
@@ -1044,47 +1044,47 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.6606</v>
+        <v>3.6461</v>
       </c>
       <c r="C14" t="n">
-        <v>2.4665</v>
+        <v>2.4568</v>
       </c>
       <c r="D14" t="n">
-        <v>1.0422</v>
+        <v>1.0148</v>
       </c>
       <c r="E14" t="n">
-        <v>3.6606</v>
+        <v>3.6461</v>
       </c>
       <c r="F14" t="n">
-        <v>2.4958</v>
+        <v>4.0071</v>
       </c>
       <c r="G14" t="n">
-        <v>1.1648</v>
+        <v>-0.5575</v>
       </c>
       <c r="H14" t="n">
-        <v>3.3402</v>
+        <v>6.0453</v>
       </c>
       <c r="I14" t="n">
-        <v>1.8037</v>
+        <v>6.3609</v>
       </c>
       <c r="J14" t="n">
-        <v>1.1648</v>
+        <v>-0.5575</v>
       </c>
       <c r="K14" t="n">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="L14" t="n">
-        <v>154</v>
+        <v>43</v>
       </c>
       <c r="M14" t="n">
-        <v>2.9685</v>
+        <v>5.8034</v>
       </c>
       <c r="N14" t="n">
-        <v>304</v>
+        <v>200</v>
       </c>
     </row>
     <row r="15">
@@ -1094,16 +1094,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.544</v>
+        <v>3.6354</v>
       </c>
       <c r="C15" t="n">
-        <v>2.388</v>
+        <v>2.4496</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9891</v>
+        <v>1.01</v>
       </c>
       <c r="E15" t="n">
-        <v>3.544</v>
+        <v>3.6354</v>
       </c>
       <c r="F15" t="n">
         <v>2.8063</v>
@@ -1136,47 +1136,47 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>ultimate</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.4496</v>
+        <v>3.5659</v>
       </c>
       <c r="C16" t="n">
-        <v>2.3244</v>
+        <v>2.4027</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9461000000000001</v>
+        <v>0.979</v>
       </c>
       <c r="E16" t="n">
-        <v>3.4496</v>
+        <v>3.5659</v>
       </c>
       <c r="F16" t="n">
-        <v>4.0071</v>
+        <v>3.1713</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.5575</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>6.0453</v>
+        <v>4.2162</v>
       </c>
       <c r="I16" t="n">
-        <v>6.3609</v>
+        <v>4.3248</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.5575</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>157</v>
+        <v>214</v>
       </c>
       <c r="L16" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>5.8034</v>
+        <v>4.3248</v>
       </c>
       <c r="N16" t="n">
-        <v>200</v>
+        <v>214</v>
       </c>
     </row>
     <row r="17">
@@ -1186,16 +1186,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.4383</v>
+        <v>3.5361</v>
       </c>
       <c r="C17" t="n">
-        <v>2.3168</v>
+        <v>2.3827</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.9657</v>
       </c>
       <c r="E17" t="n">
-        <v>3.4383</v>
+        <v>3.5361</v>
       </c>
       <c r="F17" t="n">
         <v>2.76</v>
@@ -1228,369 +1228,369 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.2448</v>
+        <v>3.5014</v>
       </c>
       <c r="C18" t="n">
-        <v>2.1864</v>
+        <v>2.3593</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8529</v>
+        <v>0.9502</v>
       </c>
       <c r="E18" t="n">
-        <v>3.2448</v>
+        <v>3.5014</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5711</v>
+        <v>2.4958</v>
       </c>
       <c r="G18" t="n">
-        <v>1.6737</v>
+        <v>1.1648</v>
       </c>
       <c r="H18" t="n">
-        <v>1.5711</v>
+        <v>3.3402</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5711</v>
+        <v>1.8037</v>
       </c>
       <c r="J18" t="n">
-        <v>1.6737</v>
+        <v>1.1648</v>
       </c>
       <c r="K18" t="n">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="L18" t="n">
-        <v>97</v>
+        <v>154</v>
       </c>
       <c r="M18" t="n">
-        <v>3.2448</v>
+        <v>2.9685</v>
       </c>
       <c r="N18" t="n">
-        <v>256</v>
+        <v>304</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ultimate</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.1713</v>
+        <v>3.4558</v>
       </c>
       <c r="C19" t="n">
-        <v>2.1368</v>
+        <v>2.3285</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8194</v>
+        <v>0.9298</v>
       </c>
       <c r="E19" t="n">
-        <v>3.1713</v>
+        <v>3.4558</v>
       </c>
       <c r="F19" t="n">
-        <v>3.1713</v>
+        <v>1.5711</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1.6737</v>
       </c>
       <c r="H19" t="n">
-        <v>4.2162</v>
+        <v>1.5711</v>
       </c>
       <c r="I19" t="n">
-        <v>4.3248</v>
+        <v>1.5711</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1.6737</v>
       </c>
       <c r="K19" t="n">
-        <v>214</v>
+        <v>159</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="M19" t="n">
-        <v>4.3248</v>
+        <v>3.2448</v>
       </c>
       <c r="N19" t="n">
-        <v>214</v>
+        <v>256</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>torzsi</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.1495</v>
+        <v>3.3407</v>
       </c>
       <c r="C20" t="n">
-        <v>2.1222</v>
+        <v>2.251</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8095</v>
+        <v>0.8784</v>
       </c>
       <c r="E20" t="n">
-        <v>3.1495</v>
+        <v>3.3407</v>
       </c>
       <c r="F20" t="n">
-        <v>2.6659</v>
+        <v>2.5584</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4836</v>
+        <v>0.5854</v>
       </c>
       <c r="H20" t="n">
-        <v>3.1099</v>
+        <v>2.8745</v>
       </c>
       <c r="I20" t="n">
-        <v>3.3566</v>
+        <v>2.8745</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4836</v>
+        <v>0.5854</v>
       </c>
       <c r="K20" t="n">
-        <v>246</v>
+        <v>159</v>
       </c>
       <c r="L20" t="n">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="M20" t="n">
-        <v>3.8402</v>
+        <v>3.4599</v>
       </c>
       <c r="N20" t="n">
-        <v>319</v>
+        <v>256</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>torzsi</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3.1438</v>
+        <v>3.2877</v>
       </c>
       <c r="C21" t="n">
-        <v>2.1183</v>
+        <v>2.2153</v>
       </c>
       <c r="D21" t="n">
-        <v>0.8069</v>
+        <v>0.8547</v>
       </c>
       <c r="E21" t="n">
-        <v>3.1438</v>
+        <v>3.2877</v>
       </c>
       <c r="F21" t="n">
-        <v>2.5584</v>
+        <v>3.0124</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5854</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>2.8745</v>
+        <v>3.8682</v>
       </c>
       <c r="I21" t="n">
-        <v>2.8745</v>
+        <v>3.9679</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5854</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>159</v>
+        <v>214</v>
       </c>
       <c r="L21" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4599</v>
+        <v>3.9679</v>
       </c>
       <c r="N21" t="n">
-        <v>256</v>
+        <v>214</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3.0124</v>
+        <v>3.2147</v>
       </c>
       <c r="C22" t="n">
-        <v>2.0298</v>
+        <v>2.1661</v>
       </c>
       <c r="D22" t="n">
-        <v>0.7471</v>
+        <v>0.8221000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>3.0124</v>
+        <v>3.2147</v>
       </c>
       <c r="F22" t="n">
-        <v>3.0124</v>
+        <v>2.6659</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>0.4836</v>
       </c>
       <c r="H22" t="n">
-        <v>3.8682</v>
+        <v>3.1099</v>
       </c>
       <c r="I22" t="n">
-        <v>3.9679</v>
+        <v>3.3566</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>0.4836</v>
       </c>
       <c r="K22" t="n">
-        <v>214</v>
+        <v>246</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="M22" t="n">
-        <v>3.9679</v>
+        <v>3.8402</v>
       </c>
       <c r="N22" t="n">
-        <v>214</v>
+        <v>319</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>w0nderful</t>
+          <t>nqz</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.9269</v>
+        <v>3.1464</v>
       </c>
       <c r="C23" t="n">
-        <v>1.9722</v>
+        <v>2.1201</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7082000000000001</v>
+        <v>0.7916</v>
       </c>
       <c r="E23" t="n">
-        <v>2.9269</v>
+        <v>3.1464</v>
       </c>
       <c r="F23" t="n">
-        <v>2.7948</v>
+        <v>2.8851</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1321</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>4.3269</v>
+        <v>3.5897</v>
       </c>
       <c r="I23" t="n">
-        <v>2.3365</v>
+        <v>3.5897</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1321</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>127</v>
+        <v>207</v>
       </c>
       <c r="L23" t="n">
-        <v>171</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>2.4686</v>
+        <v>3.5897</v>
       </c>
       <c r="N23" t="n">
-        <v>298</v>
+        <v>207</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>nqz</t>
+          <t>w0nderful</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.8851</v>
+        <v>2.9543</v>
       </c>
       <c r="C24" t="n">
-        <v>1.944</v>
+        <v>1.9906</v>
       </c>
       <c r="D24" t="n">
-        <v>0.6892</v>
+        <v>0.7058</v>
       </c>
       <c r="E24" t="n">
-        <v>2.8851</v>
+        <v>2.9543</v>
       </c>
       <c r="F24" t="n">
-        <v>2.8851</v>
+        <v>2.7948</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>0.1321</v>
       </c>
       <c r="H24" t="n">
-        <v>3.5897</v>
+        <v>4.3269</v>
       </c>
       <c r="I24" t="n">
-        <v>3.5897</v>
+        <v>2.3365</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>0.1321</v>
       </c>
       <c r="K24" t="n">
-        <v>207</v>
+        <v>127</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>171</v>
       </c>
       <c r="M24" t="n">
-        <v>3.5897</v>
+        <v>2.4686</v>
       </c>
       <c r="N24" t="n">
-        <v>207</v>
+        <v>298</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.8234</v>
+        <v>2.9414</v>
       </c>
       <c r="C25" t="n">
-        <v>1.9024</v>
+        <v>1.9819</v>
       </c>
       <c r="D25" t="n">
-        <v>0.6611</v>
+        <v>0.7</v>
       </c>
       <c r="E25" t="n">
-        <v>2.8234</v>
+        <v>2.9414</v>
       </c>
       <c r="F25" t="n">
-        <v>2.4328</v>
+        <v>2.5801</v>
       </c>
       <c r="G25" t="n">
-        <v>0.3906</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>3.1325</v>
+        <v>2.9221</v>
       </c>
       <c r="I25" t="n">
-        <v>1.6915</v>
+        <v>2.9221</v>
       </c>
       <c r="J25" t="n">
-        <v>0.3906</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>127</v>
+        <v>154</v>
       </c>
       <c r="L25" t="n">
-        <v>171</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>2.0821</v>
+        <v>2.9221</v>
       </c>
       <c r="N25" t="n">
-        <v>298</v>
+        <v>154</v>
       </c>
     </row>
     <row r="26">
@@ -1600,16 +1600,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.6879</v>
+        <v>2.8174</v>
       </c>
       <c r="C26" t="n">
-        <v>1.8111</v>
+        <v>1.8984</v>
       </c>
       <c r="D26" t="n">
-        <v>0.5994</v>
+        <v>0.6447000000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>2.6879</v>
+        <v>2.8174</v>
       </c>
       <c r="F26" t="n">
         <v>2.6879</v>
@@ -1642,93 +1642,93 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.5801</v>
+        <v>2.7117</v>
       </c>
       <c r="C27" t="n">
-        <v>1.7385</v>
+        <v>1.8272</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5503</v>
+        <v>0.5974</v>
       </c>
       <c r="E27" t="n">
-        <v>2.5801</v>
+        <v>2.7117</v>
       </c>
       <c r="F27" t="n">
-        <v>2.5801</v>
+        <v>2.5343</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>2.9221</v>
+        <v>2.8219</v>
       </c>
       <c r="I27" t="n">
-        <v>2.9221</v>
+        <v>2.8219</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>154</v>
+        <v>131</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>2.9221</v>
+        <v>2.8219</v>
       </c>
       <c r="N27" t="n">
-        <v>154</v>
+        <v>131</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.5343</v>
+        <v>2.6044</v>
       </c>
       <c r="C28" t="n">
-        <v>1.7076</v>
+        <v>1.7549</v>
       </c>
       <c r="D28" t="n">
-        <v>0.5295</v>
+        <v>0.5495</v>
       </c>
       <c r="E28" t="n">
-        <v>2.5343</v>
+        <v>2.6044</v>
       </c>
       <c r="F28" t="n">
-        <v>2.5343</v>
+        <v>2.4328</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>0.3906</v>
       </c>
       <c r="H28" t="n">
-        <v>2.8219</v>
+        <v>3.1325</v>
       </c>
       <c r="I28" t="n">
-        <v>2.8219</v>
+        <v>1.6915</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.3906</v>
       </c>
       <c r="K28" t="n">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>171</v>
       </c>
       <c r="M28" t="n">
-        <v>2.8219</v>
+        <v>2.0821</v>
       </c>
       <c r="N28" t="n">
-        <v>131</v>
+        <v>298</v>
       </c>
     </row>
     <row r="29">
@@ -1738,16 +1738,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.4659</v>
+        <v>2.5729</v>
       </c>
       <c r="C29" t="n">
-        <v>1.6615</v>
+        <v>1.7336</v>
       </c>
       <c r="D29" t="n">
-        <v>0.4983</v>
+        <v>0.5354</v>
       </c>
       <c r="E29" t="n">
-        <v>2.4659</v>
+        <v>2.5729</v>
       </c>
       <c r="F29" t="n">
         <v>2.3478</v>
@@ -1784,16 +1784,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.2508</v>
+        <v>2.212</v>
       </c>
       <c r="C30" t="n">
-        <v>1.5166</v>
+        <v>1.4905</v>
       </c>
       <c r="D30" t="n">
-        <v>0.4004</v>
+        <v>0.3742</v>
       </c>
       <c r="E30" t="n">
-        <v>2.2508</v>
+        <v>2.212</v>
       </c>
       <c r="F30" t="n">
         <v>-1.0863</v>
@@ -1830,16 +1830,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2.2359</v>
+        <v>2.1844</v>
       </c>
       <c r="C31" t="n">
-        <v>1.5066</v>
+        <v>1.4719</v>
       </c>
       <c r="D31" t="n">
-        <v>0.3936</v>
+        <v>0.3619</v>
       </c>
       <c r="E31" t="n">
-        <v>2.2359</v>
+        <v>2.1844</v>
       </c>
       <c r="F31" t="n">
         <v>2.2359</v>
@@ -1876,16 +1876,16 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.8981</v>
+        <v>1.9083</v>
       </c>
       <c r="C32" t="n">
-        <v>1.279</v>
+        <v>1.2858</v>
       </c>
       <c r="D32" t="n">
-        <v>0.2399</v>
+        <v>0.2386</v>
       </c>
       <c r="E32" t="n">
-        <v>1.8981</v>
+        <v>1.9083</v>
       </c>
       <c r="F32" t="n">
         <v>1.8981</v>
@@ -1922,16 +1922,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.8001</v>
+        <v>1.8446</v>
       </c>
       <c r="C33" t="n">
-        <v>1.2129</v>
+        <v>1.2429</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1952</v>
+        <v>0.2101</v>
       </c>
       <c r="E33" t="n">
-        <v>1.8001</v>
+        <v>1.8446</v>
       </c>
       <c r="F33" t="n">
         <v>1.8001</v>
@@ -1964,369 +1964,369 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Techno</t>
+          <t>lux</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.7847</v>
+        <v>1.7614</v>
       </c>
       <c r="C34" t="n">
-        <v>1.2025</v>
+        <v>1.1868</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1882</v>
+        <v>0.173</v>
       </c>
       <c r="E34" t="n">
-        <v>1.7847</v>
+        <v>1.7614</v>
       </c>
       <c r="F34" t="n">
-        <v>1.7847</v>
+        <v>1.6903</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1.7847</v>
+        <v>1.6903</v>
       </c>
       <c r="I34" t="n">
-        <v>1.7847</v>
+        <v>1.6903</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>191</v>
+        <v>207</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1.7847</v>
+        <v>1.6903</v>
       </c>
       <c r="N34" t="n">
-        <v>191</v>
+        <v>207</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>lux</t>
+          <t>Techno</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.6903</v>
+        <v>1.7461</v>
       </c>
       <c r="C35" t="n">
-        <v>1.1389</v>
+        <v>1.1765</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1453</v>
+        <v>0.1661</v>
       </c>
       <c r="E35" t="n">
-        <v>1.6903</v>
+        <v>1.7461</v>
       </c>
       <c r="F35" t="n">
-        <v>1.6903</v>
+        <v>1.7847</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1.6903</v>
+        <v>1.7847</v>
       </c>
       <c r="I35" t="n">
-        <v>1.6903</v>
+        <v>1.7847</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>207</v>
+        <v>191</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1.6903</v>
+        <v>1.7847</v>
       </c>
       <c r="N35" t="n">
-        <v>207</v>
+        <v>191</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>story</t>
+          <t>fame</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.5907</v>
+        <v>1.5751</v>
       </c>
       <c r="C36" t="n">
-        <v>1.0718</v>
+        <v>1.0613</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0999</v>
+        <v>0.0897</v>
       </c>
       <c r="E36" t="n">
-        <v>1.5907</v>
+        <v>1.5751</v>
       </c>
       <c r="F36" t="n">
-        <v>1.4946</v>
+        <v>1.3953</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0961</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1.4946</v>
+        <v>1.3953</v>
       </c>
       <c r="I36" t="n">
-        <v>1.5331</v>
+        <v>1.3953</v>
       </c>
       <c r="J36" t="n">
-        <v>0.0961</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>169</v>
+        <v>133</v>
       </c>
       <c r="L36" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>1.6292</v>
+        <v>1.3953</v>
       </c>
       <c r="N36" t="n">
-        <v>279</v>
+        <v>133</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>floppy</t>
+          <t>story</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.5147</v>
+        <v>1.5569</v>
       </c>
       <c r="C37" t="n">
-        <v>1.0206</v>
+        <v>1.0491</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0653</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="E37" t="n">
-        <v>1.5147</v>
+        <v>1.5569</v>
       </c>
       <c r="F37" t="n">
-        <v>1.5147</v>
+        <v>1.4946</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>0.0961</v>
       </c>
       <c r="H37" t="n">
-        <v>1.5147</v>
+        <v>1.4946</v>
       </c>
       <c r="I37" t="n">
-        <v>1.5147</v>
+        <v>1.5331</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>0.0961</v>
       </c>
       <c r="K37" t="n">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="M37" t="n">
-        <v>1.5147</v>
+        <v>1.6292</v>
       </c>
       <c r="N37" t="n">
-        <v>154</v>
+        <v>279</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>fame</t>
+          <t>floppy</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.3953</v>
+        <v>1.3957</v>
       </c>
       <c r="C38" t="n">
-        <v>0.9402</v>
+        <v>0.9404</v>
       </c>
       <c r="D38" t="n">
-        <v>0.011</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="E38" t="n">
-        <v>1.3953</v>
+        <v>1.3957</v>
       </c>
       <c r="F38" t="n">
-        <v>1.3953</v>
+        <v>1.5147</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1.3953</v>
+        <v>1.5147</v>
       </c>
       <c r="I38" t="n">
-        <v>1.3953</v>
+        <v>1.5147</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>1.3953</v>
+        <v>1.5147</v>
       </c>
       <c r="N38" t="n">
-        <v>133</v>
+        <v>154</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>Staehr</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.3259</v>
+        <v>1.3548</v>
       </c>
       <c r="C39" t="n">
-        <v>0.8934</v>
+        <v>0.9129</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.0206</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="E39" t="n">
-        <v>1.3259</v>
+        <v>1.3548</v>
       </c>
       <c r="F39" t="n">
-        <v>1.3259</v>
+        <v>1.2629</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>1.3259</v>
+        <v>1.2629</v>
       </c>
       <c r="I39" t="n">
-        <v>1.3601</v>
+        <v>1.2629</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>214</v>
+        <v>131</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>1.3601</v>
+        <v>1.2629</v>
       </c>
       <c r="N39" t="n">
-        <v>214</v>
+        <v>131</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Staehr</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.2629</v>
+        <v>1.3304</v>
       </c>
       <c r="C40" t="n">
-        <v>0.851</v>
+        <v>0.8964</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.0493</v>
+        <v>-0.0196</v>
       </c>
       <c r="E40" t="n">
-        <v>1.2629</v>
+        <v>1.3304</v>
       </c>
       <c r="F40" t="n">
-        <v>1.2629</v>
+        <v>1.3259</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1.2629</v>
+        <v>1.3259</v>
       </c>
       <c r="I40" t="n">
-        <v>1.2629</v>
+        <v>1.3601</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>131</v>
+        <v>214</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1.2629</v>
+        <v>1.3601</v>
       </c>
       <c r="N40" t="n">
-        <v>131</v>
+        <v>214</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>SunPayus</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.14</v>
+        <v>1.1989</v>
       </c>
       <c r="C41" t="n">
-        <v>0.7681</v>
+        <v>0.8078</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.1053</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="E41" t="n">
-        <v>1.14</v>
+        <v>1.1989</v>
       </c>
       <c r="F41" t="n">
-        <v>1.14</v>
+        <v>1.1018</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>1.14</v>
+        <v>1.1018</v>
       </c>
       <c r="I41" t="n">
-        <v>1.14</v>
+        <v>1.1018</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>1.14</v>
+        <v>1.1018</v>
       </c>
       <c r="N41" t="n">
-        <v>191</v>
+        <v>179</v>
       </c>
     </row>
     <row r="42">
@@ -2336,16 +2336,16 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1.1265</v>
+        <v>1.1565</v>
       </c>
       <c r="C42" t="n">
-        <v>0.759</v>
+        <v>0.7793</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.1114</v>
+        <v>-0.09719999999999999</v>
       </c>
       <c r="E42" t="n">
-        <v>1.1265</v>
+        <v>1.1565</v>
       </c>
       <c r="F42" t="n">
         <v>1.1265</v>
@@ -2378,32 +2378,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SunPayus</t>
+          <t>Snappi</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1.1018</v>
+        <v>1.0565</v>
       </c>
       <c r="C43" t="n">
-        <v>0.7423999999999999</v>
+        <v>0.7119</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.1226</v>
+        <v>-0.1419</v>
       </c>
       <c r="E43" t="n">
-        <v>1.1018</v>
+        <v>1.0565</v>
       </c>
       <c r="F43" t="n">
-        <v>1.1018</v>
+        <v>1.0417</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>1.1018</v>
+        <v>1.0417</v>
       </c>
       <c r="I43" t="n">
-        <v>1.1018</v>
+        <v>1.0417</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2415,7 +2415,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>1.1018</v>
+        <v>1.0417</v>
       </c>
       <c r="N43" t="n">
         <v>179</v>
@@ -2424,47 +2424,47 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Snappi</t>
+          <t>910</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1.0417</v>
+        <v>1.0391</v>
       </c>
       <c r="C44" t="n">
-        <v>0.7019</v>
+        <v>0.7002</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.15</v>
+        <v>-0.1497</v>
       </c>
       <c r="E44" t="n">
-        <v>1.0417</v>
+        <v>1.0391</v>
       </c>
       <c r="F44" t="n">
-        <v>1.0417</v>
+        <v>1.14</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>1.0417</v>
+        <v>1.14</v>
       </c>
       <c r="I44" t="n">
-        <v>1.0417</v>
+        <v>1.14</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>1.0417</v>
+        <v>1.14</v>
       </c>
       <c r="N44" t="n">
-        <v>179</v>
+        <v>191</v>
       </c>
     </row>
     <row r="45">
@@ -2474,16 +2474,16 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.9789</v>
+        <v>0.8053</v>
       </c>
       <c r="C45" t="n">
-        <v>0.6596</v>
+        <v>0.5426</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.1786</v>
+        <v>-0.2541</v>
       </c>
       <c r="E45" t="n">
-        <v>0.9789</v>
+        <v>0.8053</v>
       </c>
       <c r="F45" t="n">
         <v>0.9789</v>
@@ -2516,93 +2516,93 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>snow</t>
+          <t>MartinezSa</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5051</v>
+        <v>0.616</v>
       </c>
       <c r="C46" t="n">
-        <v>0.3403</v>
+        <v>0.4151</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3943</v>
+        <v>-0.3387</v>
       </c>
       <c r="E46" t="n">
-        <v>0.5051</v>
+        <v>0.616</v>
       </c>
       <c r="F46" t="n">
-        <v>0.5051</v>
+        <v>0.4432</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.5051</v>
+        <v>0.4432</v>
       </c>
       <c r="I46" t="n">
-        <v>0.5051</v>
+        <v>0.4432</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>207</v>
+        <v>108</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.5051</v>
+        <v>0.4432</v>
       </c>
       <c r="N46" t="n">
-        <v>207</v>
+        <v>108</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MartinezSa</t>
+          <t>snow</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.4432</v>
+        <v>0.3274</v>
       </c>
       <c r="C47" t="n">
-        <v>0.2986</v>
+        <v>0.2206</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.4224</v>
+        <v>-0.4676</v>
       </c>
       <c r="E47" t="n">
-        <v>0.4432</v>
+        <v>0.3274</v>
       </c>
       <c r="F47" t="n">
-        <v>0.4432</v>
+        <v>0.5051</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.4432</v>
+        <v>0.5051</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4432</v>
+        <v>0.5051</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>108</v>
+        <v>207</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.4432</v>
+        <v>0.5051</v>
       </c>
       <c r="N47" t="n">
-        <v>108</v>
+        <v>207</v>
       </c>
     </row>
     <row r="48">
@@ -2612,16 +2612,16 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.4275</v>
+        <v>0.3208</v>
       </c>
       <c r="C48" t="n">
-        <v>0.2881</v>
+        <v>0.2162</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.4296</v>
+        <v>-0.4705</v>
       </c>
       <c r="E48" t="n">
-        <v>0.4275</v>
+        <v>0.3208</v>
       </c>
       <c r="F48" t="n">
         <v>0.9737</v>
@@ -2654,185 +2654,185 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.1974</v>
+        <v>0.2663</v>
       </c>
       <c r="C49" t="n">
-        <v>0.133</v>
+        <v>0.1794</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.5343</v>
+        <v>-0.4949</v>
       </c>
       <c r="E49" t="n">
-        <v>0.1974</v>
+        <v>0.2663</v>
       </c>
       <c r="F49" t="n">
-        <v>0.1974</v>
+        <v>0.1888</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.1974</v>
+        <v>0.1888</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1974</v>
+        <v>0.1888</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.1974</v>
+        <v>0.1888</v>
       </c>
       <c r="N49" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.1888</v>
+        <v>0.2143</v>
       </c>
       <c r="C50" t="n">
-        <v>0.1272</v>
+        <v>0.1444</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.5383</v>
+        <v>-0.5181</v>
       </c>
       <c r="E50" t="n">
-        <v>0.1888</v>
+        <v>0.2143</v>
       </c>
       <c r="F50" t="n">
-        <v>0.1888</v>
+        <v>0.1805</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.1888</v>
+        <v>0.1805</v>
       </c>
       <c r="I50" t="n">
-        <v>0.1888</v>
+        <v>0.1805</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0.1888</v>
+        <v>0.1805</v>
       </c>
       <c r="N50" t="n">
-        <v>133</v>
+        <v>179</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.1805</v>
+        <v>0.1488</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1216</v>
+        <v>0.1003</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.542</v>
+        <v>-0.5474</v>
       </c>
       <c r="E51" t="n">
-        <v>0.1805</v>
+        <v>0.1488</v>
       </c>
       <c r="F51" t="n">
-        <v>0.1805</v>
+        <v>0.1974</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.1805</v>
+        <v>0.1974</v>
       </c>
       <c r="I51" t="n">
-        <v>0.1805</v>
+        <v>0.1974</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>179</v>
+        <v>131</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0.1805</v>
+        <v>0.1974</v>
       </c>
       <c r="N51" t="n">
-        <v>179</v>
+        <v>131</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>JT</t>
+          <t>buda</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.1802</v>
+        <v>0.1359</v>
       </c>
       <c r="C52" t="n">
-        <v>0.1214</v>
+        <v>0.0916</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.5422</v>
+        <v>-0.5531</v>
       </c>
       <c r="E52" t="n">
-        <v>0.1802</v>
+        <v>0.1359</v>
       </c>
       <c r="F52" t="n">
-        <v>0.1802</v>
+        <v>0.093</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0.1802</v>
+        <v>0.093</v>
       </c>
       <c r="I52" t="n">
-        <v>0.1802</v>
+        <v>0.093</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>154</v>
+        <v>108</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0.1802</v>
+        <v>0.093</v>
       </c>
       <c r="N52" t="n">
-        <v>154</v>
+        <v>108</v>
       </c>
     </row>
     <row r="53">
@@ -2842,16 +2842,16 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.162</v>
+        <v>0.1005</v>
       </c>
       <c r="C53" t="n">
-        <v>0.1092</v>
+        <v>0.0677</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.5505</v>
+        <v>-0.5689</v>
       </c>
       <c r="E53" t="n">
-        <v>0.162</v>
+        <v>0.1005</v>
       </c>
       <c r="F53" t="n">
         <v>0.162</v>
@@ -2884,47 +2884,47 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>buda</t>
+          <t>n0rb3r7</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.093</v>
+        <v>0.0131</v>
       </c>
       <c r="C54" t="n">
-        <v>0.06270000000000001</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.5819</v>
+        <v>-0.608</v>
       </c>
       <c r="E54" t="n">
-        <v>0.093</v>
+        <v>0.0131</v>
       </c>
       <c r="F54" t="n">
-        <v>0.093</v>
+        <v>0.0119</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.093</v>
+        <v>0.0119</v>
       </c>
       <c r="I54" t="n">
-        <v>0.093</v>
+        <v>0.0119</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>108</v>
+        <v>133</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0.093</v>
+        <v>0.0119</v>
       </c>
       <c r="N54" t="n">
-        <v>108</v>
+        <v>133</v>
       </c>
     </row>
     <row r="55">
@@ -2934,16 +2934,16 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.035</v>
+        <v>-0.0256</v>
       </c>
       <c r="C55" t="n">
-        <v>0.0236</v>
+        <v>-0.0172</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.6083</v>
+        <v>-0.6253</v>
       </c>
       <c r="E55" t="n">
-        <v>0.035</v>
+        <v>-0.0256</v>
       </c>
       <c r="F55" t="n">
         <v>0.035</v>
@@ -2976,93 +2976,93 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>n0rb3r7</t>
+          <t>skullz</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.0119</v>
+        <v>-0.0273</v>
       </c>
       <c r="C56" t="n">
-        <v>0.008</v>
+        <v>-0.0184</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.6188</v>
+        <v>-0.626</v>
       </c>
       <c r="E56" t="n">
-        <v>0.0119</v>
+        <v>-0.0273</v>
       </c>
       <c r="F56" t="n">
-        <v>0.0119</v>
+        <v>-0.442</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0.0119</v>
+        <v>-0.442</v>
       </c>
       <c r="I56" t="n">
-        <v>0.0119</v>
+        <v>-0.442</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>133</v>
+        <v>77</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0.0119</v>
+        <v>-0.442</v>
       </c>
       <c r="N56" t="n">
-        <v>133</v>
+        <v>77</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>JT</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.0286</v>
+        <v>-0.0511</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.0193</v>
+        <v>-0.0344</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.6372</v>
+        <v>-0.6366000000000001</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.0286</v>
+        <v>-0.0511</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.0286</v>
+        <v>0.1802</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.0286</v>
+        <v>0.1802</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.0286</v>
+        <v>0.1802</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.0286</v>
+        <v>0.1802</v>
       </c>
       <c r="N57" t="n">
-        <v>133</v>
+        <v>154</v>
       </c>
     </row>
     <row r="58">
@@ -3072,16 +3072,16 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.1526</v>
+        <v>-0.2115</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.1028</v>
+        <v>-0.1425</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.6937</v>
+        <v>-0.7083</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.1526</v>
+        <v>-0.2115</v>
       </c>
       <c r="F58" t="n">
         <v>-0.1526</v>
@@ -3114,93 +3114,93 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>donk</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.2042</v>
+        <v>-0.2616</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.1376</v>
+        <v>-0.1763</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.7171999999999999</v>
+        <v>-0.7307</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.2042</v>
+        <v>-0.2616</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.2042</v>
+        <v>-0.6234</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.2042</v>
+        <v>-0.6234</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2042</v>
+        <v>-0.6234</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>179</v>
+        <v>76</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.2042</v>
+        <v>-0.6234</v>
       </c>
       <c r="N59" t="n">
-        <v>179</v>
+        <v>76</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>br0</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.412</v>
+        <v>-0.2786</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.2776</v>
+        <v>-0.1877</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.8118</v>
+        <v>-0.7383</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.412</v>
+        <v>-0.2786</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.412</v>
+        <v>-0.0286</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.412</v>
+        <v>-0.0286</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.412</v>
+        <v>-0.0286</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.412</v>
+        <v>-0.0286</v>
       </c>
       <c r="N60" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="61">
@@ -3210,16 +3210,16 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.4197</v>
+        <v>-0.3041</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.2828</v>
+        <v>-0.2049</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.8153</v>
+        <v>-0.7497</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.4197</v>
+        <v>-0.3041</v>
       </c>
       <c r="F61" t="n">
         <v>-0.4197</v>
@@ -3252,170 +3252,170 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>skullz</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.442</v>
+        <v>-0.3191</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.2978</v>
+        <v>-0.215</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.8254</v>
+        <v>-0.7564</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.442</v>
+        <v>-0.3191</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.442</v>
+        <v>-0.2042</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.442</v>
+        <v>-0.2042</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.442</v>
+        <v>-0.2042</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>77</v>
+        <v>179</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.442</v>
+        <v>-0.2042</v>
       </c>
       <c r="N62" t="n">
-        <v>77</v>
+        <v>179</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MUTiRiS</t>
+          <t>br0</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.5897</v>
+        <v>-0.6062</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.3973</v>
+        <v>-0.4085</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.8925999999999999</v>
+        <v>-0.8846000000000001</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.5897</v>
+        <v>-0.6062</v>
       </c>
       <c r="F63" t="n">
-        <v>-1.3016</v>
+        <v>-0.412</v>
       </c>
       <c r="G63" t="n">
-        <v>0.7119</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-1.3016</v>
+        <v>-0.412</v>
       </c>
       <c r="I63" t="n">
-        <v>-1.3351</v>
+        <v>-0.412</v>
       </c>
       <c r="J63" t="n">
-        <v>0.7119</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>169</v>
+        <v>131</v>
       </c>
       <c r="L63" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.6232</v>
+        <v>-0.412</v>
       </c>
       <c r="N63" t="n">
-        <v>279</v>
+        <v>131</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>donk</t>
+          <t>MUTiRiS</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.6234</v>
+        <v>-0.6589</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.4201</v>
+        <v>-0.444</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.908</v>
+        <v>-0.9081</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.6234</v>
+        <v>-0.6589</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.6234</v>
+        <v>-1.3016</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>0.7119</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.6234</v>
+        <v>-1.3016</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.6234</v>
+        <v>-1.3351</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>0.7119</v>
       </c>
       <c r="K64" t="n">
-        <v>76</v>
+        <v>169</v>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.6234</v>
+        <v>-0.6232</v>
       </c>
       <c r="N64" t="n">
-        <v>76</v>
+        <v>279</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>HUASOPEEK</t>
+          <t>dgt</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.652</v>
+        <v>-0.7202</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.4393</v>
+        <v>-0.4853</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.921</v>
+        <v>-0.9355</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.652</v>
+        <v>-0.7202</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.652</v>
+        <v>-0.6717</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.652</v>
+        <v>-0.6717</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.652</v>
+        <v>-0.6717</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -3427,7 +3427,7 @@
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.652</v>
+        <v>-0.6717</v>
       </c>
       <c r="N65" t="n">
         <v>108</v>
@@ -3436,216 +3436,216 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>dgt</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.6717</v>
+        <v>-0.8033</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.4526</v>
+        <v>-0.5413</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.93</v>
+        <v>-0.9726</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.6717</v>
+        <v>-0.8033</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.6717</v>
+        <v>-0.7635999999999999</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.6717</v>
+        <v>-0.7635999999999999</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.6717</v>
+        <v>-0.7635999999999999</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>108</v>
+        <v>76</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.6717</v>
+        <v>-0.7635999999999999</v>
       </c>
       <c r="N66" t="n">
-        <v>108</v>
+        <v>76</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>HUASOPEEK</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.7145</v>
+        <v>-0.8599</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.4814</v>
+        <v>-0.5794</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.9495</v>
+        <v>-0.9979</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.7145</v>
+        <v>-0.8599</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.7145</v>
+        <v>-0.652</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.7145</v>
+        <v>-0.652</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.7145</v>
+        <v>-0.652</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>133</v>
+        <v>108</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.7145</v>
+        <v>-0.652</v>
       </c>
       <c r="N67" t="n">
-        <v>133</v>
+        <v>108</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.7277</v>
+        <v>-0.9028</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.4903</v>
+        <v>-0.6083</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.9555</v>
+        <v>-1.0171</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.7277</v>
+        <v>-0.9028</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.7277</v>
+        <v>-0.8486</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.7277</v>
+        <v>-0.8486</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.7277</v>
+        <v>-0.8486</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.7277</v>
+        <v>-0.8486</v>
       </c>
       <c r="N68" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.7635999999999999</v>
+        <v>-0.9193</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.5145</v>
+        <v>-0.6194</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.9718</v>
+        <v>-1.0245</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.7635999999999999</v>
+        <v>-0.9193</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.7635999999999999</v>
+        <v>-0.7145</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.7635999999999999</v>
+        <v>-0.7145</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.7635999999999999</v>
+        <v>-0.7145</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.7635999999999999</v>
+        <v>-0.7145</v>
       </c>
       <c r="N69" t="n">
-        <v>76</v>
+        <v>133</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.8332000000000001</v>
+        <v>-0.9654</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.5614</v>
+        <v>-0.6505</v>
       </c>
       <c r="D70" t="n">
-        <v>-1.0035</v>
+        <v>-1.045</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.8332000000000001</v>
+        <v>-0.9654</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.8332000000000001</v>
+        <v>-0.7277</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.8332000000000001</v>
+        <v>-0.7277</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.8332000000000001</v>
+        <v>-0.7277</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -3657,7 +3657,7 @@
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.8332000000000001</v>
+        <v>-0.7277</v>
       </c>
       <c r="N70" t="n">
         <v>77</v>
@@ -3666,47 +3666,47 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>kauez</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.8486</v>
+        <v>-1.0107</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.5718</v>
+        <v>-0.681</v>
       </c>
       <c r="D71" t="n">
-        <v>-1.0105</v>
+        <v>-1.0653</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.8486</v>
+        <v>-1.0107</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.8486</v>
+        <v>-1.0483</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.8486</v>
+        <v>-1.0483</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.8486</v>
+        <v>-1.0483</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>76</v>
+        <v>207</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.8486</v>
+        <v>-1.0483</v>
       </c>
       <c r="N71" t="n">
-        <v>76</v>
+        <v>207</v>
       </c>
     </row>
     <row r="72">
@@ -3716,16 +3716,16 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-0.8756</v>
+        <v>-1.0317</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.59</v>
+        <v>-0.6952</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.0228</v>
+        <v>-1.0747</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.8756</v>
+        <v>-1.0317</v>
       </c>
       <c r="F72" t="n">
         <v>-0.9757</v>
@@ -3758,369 +3758,369 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>kauez</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.0483</v>
+        <v>-1.1709</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.7064</v>
+        <v>-0.789</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.1014</v>
+        <v>-1.1368</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.0483</v>
+        <v>-1.1709</v>
       </c>
       <c r="F73" t="n">
-        <v>-1.0483</v>
+        <v>-0.8332000000000001</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-1.0483</v>
+        <v>-0.8332000000000001</v>
       </c>
       <c r="I73" t="n">
-        <v>-1.0483</v>
+        <v>-0.8332000000000001</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>207</v>
+        <v>77</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>-1.0483</v>
+        <v>-0.8332000000000001</v>
       </c>
       <c r="N73" t="n">
-        <v>207</v>
+        <v>77</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>zont1x</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.2874</v>
+        <v>-1.6242</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.8675</v>
+        <v>-1.0944</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.2103</v>
+        <v>-1.3393</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.2874</v>
+        <v>-1.6242</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.1626</v>
+        <v>-1.473</v>
       </c>
       <c r="G74" t="n">
-        <v>-0.1248</v>
+        <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-1.1626</v>
+        <v>-1.473</v>
       </c>
       <c r="I74" t="n">
-        <v>-1.2233</v>
+        <v>-1.473</v>
       </c>
       <c r="J74" t="n">
-        <v>-0.1248</v>
+        <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>157</v>
+        <v>76</v>
       </c>
       <c r="L74" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>-1.3481</v>
+        <v>-1.473</v>
       </c>
       <c r="N74" t="n">
-        <v>200</v>
+        <v>76</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>zont1x</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.473</v>
+        <v>-1.6657</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.9925</v>
+        <v>-1.1224</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.2947</v>
+        <v>-1.3579</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.473</v>
+        <v>-1.6657</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.473</v>
+        <v>-1.1626</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>-0.1248</v>
       </c>
       <c r="H75" t="n">
-        <v>-1.473</v>
+        <v>-1.1626</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.473</v>
+        <v>-1.2233</v>
       </c>
       <c r="J75" t="n">
-        <v>0</v>
+        <v>-0.1248</v>
       </c>
       <c r="K75" t="n">
-        <v>76</v>
+        <v>157</v>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="M75" t="n">
-        <v>-1.473</v>
+        <v>-1.3481</v>
       </c>
       <c r="N75" t="n">
-        <v>76</v>
+        <v>200</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>chopper</t>
+          <t>chelo</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.4947</v>
+        <v>-1.7259</v>
       </c>
       <c r="C76" t="n">
-        <v>-1.0071</v>
+        <v>-1.1629</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.3046</v>
+        <v>-1.3847</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.4947</v>
+        <v>-1.7259</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.4947</v>
+        <v>-1.6318</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.4947</v>
+        <v>-1.6318</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.4947</v>
+        <v>-1.6318</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>-1.4947</v>
+        <v>-1.6318</v>
       </c>
       <c r="N76" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>chelo</t>
+          <t>chopper</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.6318</v>
+        <v>-1.8815</v>
       </c>
       <c r="C77" t="n">
-        <v>-1.0995</v>
+        <v>-1.2678</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.367</v>
+        <v>-1.4542</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.6318</v>
+        <v>-1.8815</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.6318</v>
+        <v>-1.4947</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>-1.6318</v>
+        <v>-1.4947</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.6318</v>
+        <v>-1.4947</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>-1.6318</v>
+        <v>-1.4947</v>
       </c>
       <c r="N77" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>siuhy</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-1.7853</v>
+        <v>-2.0771</v>
       </c>
       <c r="C78" t="n">
-        <v>-1.203</v>
+        <v>-1.3996</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.4369</v>
+        <v>-1.5416</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.7853</v>
+        <v>-2.0771</v>
       </c>
       <c r="F78" t="n">
-        <v>-1.7853</v>
+        <v>-0.51</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>-1.4085</v>
       </c>
       <c r="H78" t="n">
-        <v>-1.7853</v>
+        <v>-0.51</v>
       </c>
       <c r="I78" t="n">
-        <v>-1.7853</v>
+        <v>-0.51</v>
       </c>
       <c r="J78" t="n">
-        <v>0</v>
+        <v>-1.4085</v>
       </c>
       <c r="K78" t="n">
-        <v>77</v>
+        <v>159</v>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="M78" t="n">
-        <v>-1.7853</v>
+        <v>-1.9185</v>
       </c>
       <c r="N78" t="n">
-        <v>77</v>
+        <v>256</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>siuhy</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-1.9185</v>
+        <v>-2.5983</v>
       </c>
       <c r="C79" t="n">
-        <v>-1.2927</v>
+        <v>-1.7508</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.4975</v>
+        <v>-1.7744</v>
       </c>
       <c r="E79" t="n">
-        <v>-1.9185</v>
+        <v>-2.5983</v>
       </c>
       <c r="F79" t="n">
-        <v>-0.51</v>
+        <v>-2.3497</v>
       </c>
       <c r="G79" t="n">
-        <v>-1.4085</v>
+        <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>-0.51</v>
+        <v>-2.3497</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.51</v>
+        <v>-2.3497</v>
       </c>
       <c r="J79" t="n">
-        <v>-1.4085</v>
+        <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>159</v>
+        <v>131</v>
       </c>
       <c r="L79" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>-1.9185</v>
+        <v>-2.3497</v>
       </c>
       <c r="N79" t="n">
-        <v>256</v>
+        <v>131</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-2.3497</v>
+        <v>-2.6011</v>
       </c>
       <c r="C80" t="n">
-        <v>-1.5832</v>
+        <v>-1.7526</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.6938</v>
+        <v>-1.7757</v>
       </c>
       <c r="E80" t="n">
-        <v>-2.3497</v>
+        <v>-2.6011</v>
       </c>
       <c r="F80" t="n">
-        <v>-2.3497</v>
+        <v>-1.7853</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>-2.3497</v>
+        <v>-1.7853</v>
       </c>
       <c r="I80" t="n">
-        <v>-2.3497</v>
+        <v>-1.7853</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="L80" t="n">
         <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>-2.3497</v>
+        <v>-1.7853</v>
       </c>
       <c r="N80" t="n">
-        <v>131</v>
+        <v>77</v>
       </c>
     </row>
     <row r="81">
@@ -4130,16 +4130,16 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-2.8138</v>
+        <v>-3.0606</v>
       </c>
       <c r="C81" t="n">
-        <v>-1.896</v>
+        <v>-2.0623</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.9051</v>
+        <v>-1.9809</v>
       </c>
       <c r="E81" t="n">
-        <v>-2.8138</v>
+        <v>-3.0606</v>
       </c>
       <c r="F81" t="n">
         <v>-0.8138</v>
